--- a/file/result/matriz7x7-iteracao10-dist2-datasetFixed1000.xlsx
+++ b/file/result/matriz7x7-iteracao10-dist2-datasetFixed1000.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/67048d52181fbb0f/Documents/Projetos/classifier-cellular-automata/file/result/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_0191D5B887E05C25A39B2711595ED87656CD0FC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E3E85BB-E361-4CD7-BC40-16B884CA1393}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_0191D5B887E05C25A39B2711595ED87656CD0FC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01CD971C-3F8D-407B-8FA5-C82E9BEC0C32}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -446,6 +446,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="12" max="12" width="13.28515625" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
